--- a/excel/MapNpcData.xlsx
+++ b/excel/MapNpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82AD649-F15F-FE40-BACF-48F6A04B773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D583120-0B08-864E-844D-66EAE358CDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MapNpcInfo" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="66">
   <si>
     <t>NpcId</t>
   </si>
@@ -401,14 +401,169 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>bool</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShowMenuPopup</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마이홈_슬라임]</t>
+    </r>
+  </si>
+  <si>
+    <t>MyhomeSlimeAppeared</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum&lt;MapType&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Positions</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Myhome</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpritePositionAndScale</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CompassUIPosition</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;float&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>343,-28.5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PowderShop</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>150</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,78,0.5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,280</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>-381,6</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,36,0.5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColliderRadius</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,145</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int;id</t>
+  </si>
+  <si>
+    <t>local_string;[NpcId][Order]</t>
+  </si>
+  <si>
+    <t>enum&lt;RequirementType&gt;</t>
+  </si>
+  <si>
+    <t>list&lt;int&gt;</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>enum&lt;NpcMenuFunctionType&gt;</t>
+  </si>
+  <si>
+    <t>MenuName</t>
+  </si>
+  <si>
+    <t>ShowRequirement</t>
+  </si>
+  <si>
+    <t>ShowRequirementValues</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>FunctionType</t>
+  </si>
+  <si>
+    <t>FunctionValue</t>
+  </si>
+  <si>
+    <t>AlwaysTrue</t>
+  </si>
+  <si>
+    <r>
+      <t>미니게임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시작</t>
+    </r>
+  </si>
+  <si>
+    <t>[파우더상점_거울]</t>
+  </si>
+  <si>
     <t>PlayPowderPortalMinigame</t>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShowMenuPopup</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -423,123 +578,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>마이홈_슬라임]</t>
-    </r>
-  </si>
-  <si>
-    <t>MyhomeSlimeAppeared</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>enum&lt;MapType&gt;</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Positions</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Myhome</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpritePositionAndScale</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CompassUIPosition</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;float&gt;</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>343,-28.5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PowderShop</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>150</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,78,0.5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,280</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>-381,6</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,36,0.5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ColliderRadius</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,145</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>int;id</t>
-  </si>
-  <si>
-    <t>local_string;[NpcId][Order]</t>
-  </si>
-  <si>
-    <t>enum&lt;RequirementType&gt;</t>
-  </si>
-  <si>
-    <t>list&lt;int&gt;</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>enum&lt;NpcMenuFunctionType&gt;</t>
-  </si>
-  <si>
-    <t>MenuName</t>
-  </si>
-  <si>
-    <t>ShowRequirement</t>
-  </si>
-  <si>
-    <t>ShowRequirementValues</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>FunctionType</t>
-  </si>
-  <si>
-    <t>FunctionValue</t>
-  </si>
-  <si>
-    <t>AlwaysTrue</t>
-  </si>
-  <si>
-    <r>
-      <t>미니게임</t>
+      <t>파우더상점</t>
     </r>
     <r>
       <rPr>
@@ -549,7 +588,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t>_</t>
     </r>
     <r>
       <rPr>
@@ -559,11 +598,19 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>시작</t>
-    </r>
-  </si>
-  <si>
-    <t>[파우더상점_거울]</t>
+      <t>구매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1070,13 +1117,13 @@
         <v>4</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
@@ -1087,13 +1134,13 @@
         <v>22</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
@@ -1104,13 +1151,13 @@
         <v>23</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="20">
         <v>40</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
@@ -1121,13 +1168,13 @@
         <v>26</v>
       </c>
       <c r="C4" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>44</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="13"/>
@@ -1163,10 +1210,10 @@
         <v>10</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1180,25 +1227,25 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="19" t="s">
         <v>34</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
       <c r="A3" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
@@ -1209,10 +1256,10 @@
         <v>3</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1253,7 +1300,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H1" s="10" t="s">
         <v>7</v>
@@ -1282,7 +1329,7 @@
         <v>24</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>6</v>
@@ -1363,7 +1410,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1387,28 +1434,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="D1" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="F1" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>55</v>
-      </c>
       <c r="H1" s="24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1416,36 +1463,36 @@
         <v>0</v>
       </c>
       <c r="B2" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="D2" s="28" t="s">
         <v>57</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>58</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>5</v>
       </c>
       <c r="F2" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="H2" s="26" t="s">
         <v>60</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6">
@@ -1455,7 +1502,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="H3" s="6"/>
     </row>

--- a/excel/MapNpcData.xlsx
+++ b/excel/MapNpcData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D583120-0B08-864E-844D-66EAE358CDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E065C7-2BDA-5148-9F4A-246640CA4CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
   <si>
     <t>NpcId</t>
   </si>
@@ -182,70 +182,6 @@
         <charset val="129"/>
       </rPr>
       <t>시작</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마이홈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>슬라임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>말걸기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>]</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1117,13 +1053,13 @@
         <v>4</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
@@ -1131,16 +1067,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
@@ -1148,33 +1084,33 @@
         <v>16</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="20">
         <v>40</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>26</v>
-      </c>
       <c r="C4" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>43</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="13"/>
@@ -1210,10 +1146,10 @@
         <v>10</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1227,39 +1163,39 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="19" t="s">
         <v>33</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
       <c r="A3" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1270,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86050EB-D00F-8A40-897C-29FC87B050D7}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
@@ -1300,7 +1236,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H1" s="10" t="s">
         <v>7</v>
@@ -1326,10 +1262,10 @@
         <v>5</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>6</v>
@@ -1342,8 +1278,8 @@
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>18</v>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>3</v>
@@ -1352,65 +1288,39 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>19</v>
+      <c r="A4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15">
-      <c r="A5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>65</v>
+      <c r="I4" s="6" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1434,28 +1344,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="D1" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="F1" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>54</v>
-      </c>
       <c r="H1" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1463,36 +1373,36 @@
         <v>0</v>
       </c>
       <c r="B2" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="D2" s="28" t="s">
         <v>56</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>57</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>5</v>
       </c>
       <c r="F2" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="H2" s="26" t="s">
         <v>59</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6">
@@ -1502,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H3" s="6"/>
     </row>

--- a/excel/MapNpcData.xlsx
+++ b/excel/MapNpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E065C7-2BDA-5148-9F4A-246640CA4CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A716F0-00BA-0142-9FB1-70ED48F88CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MapNpcInfo" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
   <si>
     <t>NpcId</t>
   </si>
@@ -543,6 +543,143 @@
         <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕상점_미카]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕상점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미카</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미카</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,78,0.4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CottonCandyShop</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕상점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>]</t>
     </r>
@@ -769,7 +906,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -818,6 +955,7 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1113,7 +1251,23 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="13"/>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="10" spans="1:5" ht="13">
       <c r="C10" s="21"/>
     </row>
@@ -1125,7 +1279,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C46EA2E-F947-224D-A4BE-A46A7E528B7A}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -1198,6 +1352,20 @@
         <v>44</v>
       </c>
     </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1206,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86050EB-D00F-8A40-897C-29FC87B050D7}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
@@ -1321,6 +1489,32 @@
       </c>
       <c r="I4" s="6" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="A5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/excel/MapNpcData.xlsx
+++ b/excel/MapNpcData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A716F0-00BA-0142-9FB1-70ED48F88CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EDBE89-36AA-BC48-8D33-2384BD151285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
   <si>
     <t>NpcId</t>
   </si>
@@ -583,6 +583,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>_</t>
@@ -602,6 +603,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>]</t>
@@ -683,6 +685,10 @@
       </rPr>
       <t>]</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>-150,-156</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -906,7 +912,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -955,7 +961,6 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1359,11 +1364,11 @@
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/excel/MapNpcData.xlsx
+++ b/excel/MapNpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EDBE89-36AA-BC48-8D33-2384BD151285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D400F6A-2C2F-524B-AAA0-56216B407B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MapNpcInfo" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
   <si>
     <t>NpcId</t>
   </si>
@@ -689,6 +689,10 @@
   </si>
   <si>
     <t>-150,-156</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1267,7 +1271,7 @@
         <v>68</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>43</v>

--- a/excel/MapNpcData.xlsx
+++ b/excel/MapNpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D400F6A-2C2F-524B-AAA0-56216B407B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008F3A25-376C-904A-A8AC-1E27C59B8C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MapNpcInfo" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="75">
   <si>
     <t>NpcId</t>
   </si>
@@ -496,9 +496,6 @@
     </r>
   </si>
   <si>
-    <t>[파우더상점_거울]</t>
-  </si>
-  <si>
     <t>PlayPowderPortalMinigame</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -693,6 +690,90 @@
   </si>
   <si>
     <t>50</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayCottonCandyMinigame</t>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕상점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜사탕기계]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더상점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1262,16 +1343,16 @@
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>68</v>
-      </c>
       <c r="D5" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>43</v>
@@ -1363,16 +1444,16 @@
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1497,12 +1578,12 @@
         <v>12</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>18</v>
@@ -1523,7 +1604,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1534,7 +1615,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C47EBB-6A27-BC46-836F-0B164FBA73C0}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -1599,7 +1680,7 @@
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="6" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>61</v>
@@ -1615,9 +1696,29 @@
         <v>1</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:8" ht="15">
+      <c r="A4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/excel/MapNpcData.xlsx
+++ b/excel/MapNpcData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008F3A25-376C-904A-A8AC-1E27C59B8C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265B7387-5070-AA4C-A6BA-1E56DB361837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -707,6 +707,52 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
+      <t>파우더상점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
       <t>솜사탕상점</t>
     </r>
     <r>
@@ -726,53 +772,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>솜사탕기계]</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>파우더상점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>거울</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>]</t>
+      <t>축음기]</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>61</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>61</v>

--- a/excel/MapNpcData.xlsx
+++ b/excel/MapNpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265B7387-5070-AA4C-A6BA-1E56DB361837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F988B063-8151-EB47-A672-73BBBE617647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="3540" windowWidth="22000" windowHeight="12220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MapNpcInfo" sheetId="1" r:id="rId1"/>
@@ -685,10 +685,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>-150,-156</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>50</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -774,6 +770,10 @@
       </rPr>
       <t>축음기]</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>-193,-220</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1352,7 +1352,7 @@
         <v>67</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>43</v>
@@ -1453,7 +1453,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>61</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>61</v>
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
